--- a/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -663,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,45; 66,23</t>
+          <t>50,63; 66,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,98; 76,81</t>
+          <t>60,22; 76,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,18; 69,43</t>
+          <t>51,43; 69,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 60,4</t>
+          <t>65,83; 92,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,64; 70,91</t>
+          <t>54,34; 70,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,67; 75,87</t>
+          <t>58,63; 75,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,33; 71,56</t>
+          <t>56,29; 72,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 40,83</t>
+          <t>55,82; 90,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,42; 66,44</t>
+          <t>54,64; 66,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 74,22</t>
+          <t>62,98; 74,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,66; 68,2</t>
+          <t>56,1; 68,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 45,22</t>
+          <t>66,46; 87,9</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,67; 68,26</t>
+          <t>51,18; 68,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,14; 73,7</t>
+          <t>56,55; 73,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,86; 70,03</t>
+          <t>53,82; 69,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 67,34</t>
+          <t>55,28; 94,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,26; 68,83</t>
+          <t>51,64; 69,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,17; 66,89</t>
+          <t>49,9; 66,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,06; 68,49</t>
+          <t>52,02; 68,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 59,01</t>
+          <t>63,78; 96,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,93; 65,77</t>
+          <t>52,93; 65,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,02; 67,75</t>
+          <t>56,4; 68,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,05; 66,9</t>
+          <t>55,52; 66,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,04; 57,18</t>
+          <t>68,58; 93,11</t>
         </is>
       </c>
     </row>
@@ -943,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,02; 79,7</t>
+          <t>61,21; 80,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,97; 77,6</t>
+          <t>61,9; 78,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,68; 75,82</t>
+          <t>54,38; 75,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>26,97; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,94; 79,44</t>
+          <t>64,05; 79,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,76; 81,77</t>
+          <t>65,49; 81,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,51; 69,51</t>
+          <t>48,99; 68,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 61,98</t>
+          <t>34,54; 82,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,32; 77,4</t>
+          <t>65,12; 77,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,04; 77,63</t>
+          <t>66,14; 77,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,98; 69,88</t>
+          <t>55,85; 70,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 50,75</t>
+          <t>39,0; 81,68</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,61; 67,7</t>
+          <t>55,38; 67,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,61; 64,84</t>
+          <t>52,89; 64,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,23; 71,53</t>
+          <t>61,47; 71,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,35; 56,76</t>
+          <t>57,99; 85,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,34; 69,69</t>
+          <t>58,75; 69,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,79; 68,12</t>
+          <t>57,61; 67,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,2; 72,29</t>
+          <t>61,2; 71,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 41,73</t>
+          <t>67,48; 89,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,53; 66,97</t>
+          <t>58,8; 66,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,25; 64,91</t>
+          <t>57,38; 64,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,59; 70,47</t>
+          <t>62,68; 70,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,96; 43,14</t>
+          <t>69,42; 85,34</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,17; 67,27</t>
+          <t>51,45; 68,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,08; 75,53</t>
+          <t>62,69; 75,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,91; 75,55</t>
+          <t>62,86; 75,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,47; 57,07</t>
+          <t>63,3; 92,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,7; 72,36</t>
+          <t>57,57; 72,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,04; 73,94</t>
+          <t>60,09; 74,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,91; 77,94</t>
+          <t>64,98; 77,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 64,73</t>
+          <t>73,31; 92,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,76; 67,97</t>
+          <t>57,19; 68,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,43; 73,07</t>
+          <t>63,8; 72,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,61; 75,12</t>
+          <t>65,38; 74,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 56,68</t>
+          <t>73,76; 90,41</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,46; 80,33</t>
+          <t>63,68; 80,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,55; 72,05</t>
+          <t>49,41; 72,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,64; 64,93</t>
+          <t>42,77; 65,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,87; 66,51</t>
+          <t>50,65; 95,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56,34; 74,55</t>
+          <t>57,08; 74,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,83; 71,26</t>
+          <t>52,19; 70,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,98; 70,44</t>
+          <t>50,65; 71,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 49,19</t>
+          <t>50,92; 94,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,03; 75,23</t>
+          <t>62,43; 75,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54,3; 68,88</t>
+          <t>54,47; 68,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,08; 64,99</t>
+          <t>50,14; 65,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 49,85</t>
+          <t>62,07; 92,7</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,42; 65,78</t>
+          <t>59,49; 65,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,0; 68,2</t>
+          <t>62,07; 68,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,41; 67,5</t>
+          <t>61,39; 67,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,01; 45,87</t>
+          <t>70,51; 84,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,74; 67,91</t>
+          <t>61,56; 67,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,12; 68,24</t>
+          <t>62,04; 68,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,92; 68,23</t>
+          <t>61,9; 68,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 40,47</t>
+          <t>72,83; 85,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,44; 65,97</t>
+          <t>61,58; 66,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63,27; 67,64</t>
+          <t>62,89; 67,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,71; 67,15</t>
+          <t>62,56; 67,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,22; 40,03</t>
+          <t>74,61; 83,32</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>55105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58296</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46648</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19972</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54187</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58099</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59371</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>15497</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>109293</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>116394</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>106019</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35469</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>47847; 63134</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50524; 64425</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39469; 53358</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16307; 22862</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>46791; 60972</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>50343; 64824</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52324; 66977</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11465; 18584</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>98694; 120022</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>106903; 126688</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>95205; 115844</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>30115; 39830</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>47836</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58604</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8437</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45482</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51932</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59057</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13839</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>93318</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>110536</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>118988</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22276</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>41091; 54922</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50565; 66099</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>51903; 67031</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5799; 9902</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>38923; 52001</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>44011; 58673</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>50916; 67316</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10329; 15603</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>82388; 102522</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>100178; 121340</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>107886; 129259</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>18303; 24848</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>42789</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2652</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61455</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61331</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40567</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6612</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>104244</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>118915</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75969</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9264</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>36778; 48162</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50534; 63886</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29146; 40383</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>921; 3415</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>54756; 67705</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>54334; 67388</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>33068; 46321</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3774; 9032</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>94799; 113262</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>108862; 127380</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>67637; 84832</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5593; 11713</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>106143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>113842</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137956</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22145</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>113156</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>136827</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>126475</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>33345</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>219298</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>250669</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>264430</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>55491</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>95498; 115558</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101864; 124061</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>127478; 149274</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17513; 25721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>103690; 122943</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>124829; 147293</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>115675; 136079</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27756; 36698</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>205178; 232683</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>234826; 265997</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>248443; 278856</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>49516; 60873</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>50856</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>94946</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87112</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16608</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90539</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92682</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25337</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>117908</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>185485</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>179794</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>41946</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>44167; 58725</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>85861; 103776</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>78959; 95245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12940; 18837</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>59120; 74148</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>80798; 99537</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>84101; 100728</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>21919; 27789</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>107823; 129346</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>173185; 197191</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>166755; 190667</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>37132; 45516</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>49953</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32449</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7519</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>43532</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>43548</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>37570</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>9388</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>93485</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>75998</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>68124</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>16908</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>43796; 55690</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26019; 38115</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>24086; 36788</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4739; 8953</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>37888; 49667</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36584; 49687</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>31114; 43855</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5942; 11076</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>84371; 101435</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>66861; 84577</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>59031; 77046</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>13052; 19493</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>352682</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>415722</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>397602</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>77333</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>384863</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>442275</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>415722</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>104019</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>737544</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>857997</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>813324</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>181353</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>334281; 370526</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>395498; 434322</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>378225; 417870</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>69582; 83206</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>364758; 401910</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>420782; 462809</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>395025; 437615</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>94941; 110961</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>710863; 763470</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>827226; 885900</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>784716; 840387</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>170886; 190848</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,63; 66,81</t>
+          <t>50,25; 66,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,22; 76,79</t>
+          <t>59,82; 76,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 69,53</t>
+          <t>51,45; 69,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 92,29</t>
+          <t>63,19; 91,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,34; 70,8</t>
+          <t>53,8; 70,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,63; 75,5</t>
+          <t>58,68; 75,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,29; 72,06</t>
+          <t>55,97; 71,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,82; 90,49</t>
+          <t>55,01; 89,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,64; 66,45</t>
+          <t>54,55; 66,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,98; 74,63</t>
+          <t>61,69; 73,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 68,27</t>
+          <t>56,24; 68,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,46; 87,9</t>
+          <t>65,72; 88,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,18; 68,41</t>
+          <t>50,87; 68,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,55; 73,92</t>
+          <t>57,04; 73,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,82; 69,51</t>
+          <t>53,86; 69,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,28; 94,38</t>
+          <t>51,23; 94,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,64; 69,0</t>
+          <t>50,6; 68,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,9; 66,53</t>
+          <t>49,79; 66,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,02; 68,77</t>
+          <t>50,62; 67,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,78; 96,34</t>
+          <t>68,25; 96,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,93; 65,87</t>
+          <t>54,09; 66,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,4; 68,32</t>
+          <t>56,45; 68,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,52; 66,52</t>
+          <t>55,23; 66,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,58; 93,11</t>
+          <t>70,43; 93,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,21; 80,15</t>
+          <t>61,32; 79,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,9; 78,26</t>
+          <t>61,62; 78,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,38; 75,35</t>
+          <t>55,33; 75,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 100,0</t>
+          <t>24,78; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,05; 79,2</t>
+          <t>63,6; 79,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,49; 81,23</t>
+          <t>65,36; 81,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,99; 68,62</t>
+          <t>50,02; 69,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,54; 82,67</t>
+          <t>33,75; 83,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,12; 77,8</t>
+          <t>65,36; 77,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,14; 77,39</t>
+          <t>66,98; 78,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,85; 70,05</t>
+          <t>55,62; 69,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,0; 81,68</t>
+          <t>40,06; 82,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,38; 67,02</t>
+          <t>55,71; 67,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,89; 64,42</t>
+          <t>53,36; 65,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,47; 71,98</t>
+          <t>61,19; 71,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,99; 85,16</t>
+          <t>59,31; 85,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,75; 69,66</t>
+          <t>58,16; 69,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,61; 67,98</t>
+          <t>57,97; 68,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,2; 71,99</t>
+          <t>60,91; 72,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,48; 89,22</t>
+          <t>68,66; 88,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,8; 66,69</t>
+          <t>58,34; 66,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,38; 64,99</t>
+          <t>57,67; 65,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,68; 70,35</t>
+          <t>62,89; 70,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,42; 85,34</t>
+          <t>68,4; 85,31</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,45; 68,41</t>
+          <t>50,24; 67,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,69; 75,77</t>
+          <t>61,95; 74,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,86; 75,83</t>
+          <t>62,52; 75,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,3; 92,15</t>
+          <t>63,34; 92,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,57; 72,2</t>
+          <t>58,3; 73,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,09; 74,02</t>
+          <t>60,17; 74,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,98; 77,82</t>
+          <t>64,91; 77,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,31; 92,94</t>
+          <t>71,88; 92,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,19; 68,6</t>
+          <t>56,76; 67,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,8; 72,65</t>
+          <t>63,48; 72,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,38; 74,76</t>
+          <t>65,79; 75,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,76; 90,41</t>
+          <t>72,87; 89,91</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,68; 80,98</t>
+          <t>63,75; 80,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,41; 72,38</t>
+          <t>48,48; 71,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,77; 65,33</t>
+          <t>43,31; 65,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,65; 95,69</t>
+          <t>52,88; 95,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57,08; 74,83</t>
+          <t>54,93; 74,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,19; 70,89</t>
+          <t>51,63; 71,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,65; 71,39</t>
+          <t>51,15; 71,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50,92; 94,9</t>
+          <t>49,17; 95,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,43; 75,06</t>
+          <t>62,61; 75,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54,47; 68,9</t>
+          <t>55,13; 69,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,14; 65,44</t>
+          <t>50,07; 64,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,07; 92,7</t>
+          <t>61,29; 91,67</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,49; 65,94</t>
+          <t>59,5; 66,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,07; 68,17</t>
+          <t>62,08; 68,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,39; 67,83</t>
+          <t>61,36; 67,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,51; 84,32</t>
+          <t>70,57; 84,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,56; 67,83</t>
+          <t>61,76; 68,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,23</t>
+          <t>62,3; 68,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,9; 68,57</t>
+          <t>61,77; 68,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,83; 85,12</t>
+          <t>73,45; 85,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,58; 66,13</t>
+          <t>61,57; 66,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,89; 67,35</t>
+          <t>62,99; 67,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,56; 67,0</t>
+          <t>62,64; 67,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,61; 83,32</t>
+          <t>74,13; 83,1</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47847; 63134</t>
+          <t>47489; 62570</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50524; 64425</t>
+          <t>50185; 64370</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39469; 53358</t>
+          <t>39486; 53074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16307; 22862</t>
+          <t>15654; 22684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46791; 60972</t>
+          <t>46331; 60789</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50343; 64824</t>
+          <t>50383; 64688</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52324; 66977</t>
+          <t>52023; 66854</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11465; 18584</t>
+          <t>11297; 18460</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98694; 120022</t>
+          <t>98519; 120042</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106903; 126688</t>
+          <t>104714; 125059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95205; 115844</t>
+          <t>95431; 115606</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30115; 39830</t>
+          <t>29780; 40031</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41091; 54922</t>
+          <t>40839; 54846</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50565; 66099</t>
+          <t>51001; 65461</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51903; 67031</t>
+          <t>51934; 66985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5799; 9902</t>
+          <t>5375; 9883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38923; 52001</t>
+          <t>38133; 51760</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44011; 58673</t>
+          <t>43910; 58829</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50916; 67316</t>
+          <t>49548; 66334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10329; 15603</t>
+          <t>11054; 15598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82388; 102522</t>
+          <t>84197; 102958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100178; 121340</t>
+          <t>100259; 121369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107886; 129259</t>
+          <t>107321; 129728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18303; 24848</t>
+          <t>18797; 24849</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36778; 48162</t>
+          <t>36845; 48049</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50534; 63886</t>
+          <t>50303; 64399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29146; 40383</t>
+          <t>29651; 40691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>921; 3415</t>
+          <t>846; 3415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54756; 67705</t>
+          <t>54368; 67679</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54334; 67388</t>
+          <t>54226; 67633</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33068; 46321</t>
+          <t>33765; 46754</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3774; 9032</t>
+          <t>3687; 9111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94799; 113262</t>
+          <t>95143; 112798</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108862; 127380</t>
+          <t>110249; 128698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67637; 84832</t>
+          <t>67351; 84145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5593; 11713</t>
+          <t>5745; 11866</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95498; 115558</t>
+          <t>96061; 115826</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101864; 124061</t>
+          <t>102770; 125212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127478; 149274</t>
+          <t>126904; 148697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17513; 25721</t>
+          <t>17914; 25882</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103690; 122943</t>
+          <t>102639; 122183</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124829; 147293</t>
+          <t>125607; 147793</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115675; 136079</t>
+          <t>115127; 136128</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27756; 36698</t>
+          <t>28240; 36549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>205178; 232683</t>
+          <t>203570; 232483</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>234826; 265997</t>
+          <t>236033; 267528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>248443; 278856</t>
+          <t>249295; 279764</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49516; 60873</t>
+          <t>48788; 60851</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44167; 58725</t>
+          <t>43126; 57816</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85861; 103776</t>
+          <t>84851; 102715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78959; 95245</t>
+          <t>78529; 94953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12940; 18837</t>
+          <t>12949; 18946</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59120; 74148</t>
+          <t>59875; 75031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80798; 99537</t>
+          <t>80911; 99542</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84101; 100728</t>
+          <t>84021; 100688</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21919; 27789</t>
+          <t>21493; 27710</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107823; 129346</t>
+          <t>107017; 128154</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173185; 197191</t>
+          <t>172294; 197639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166755; 190667</t>
+          <t>167790; 191515</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37132; 45516</t>
+          <t>36683; 45264</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43796; 55690</t>
+          <t>43842; 55238</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26019; 38115</t>
+          <t>25529; 37652</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24086; 36788</t>
+          <t>24385; 37049</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4739; 8953</t>
+          <t>4948; 8948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37888; 49667</t>
+          <t>36459; 49619</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36584; 49687</t>
+          <t>36190; 50387</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31114; 43855</t>
+          <t>31422; 43665</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5942; 11076</t>
+          <t>5738; 11101</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84371; 101435</t>
+          <t>84617; 101862</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66861; 84577</t>
+          <t>67678; 84854</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59031; 77046</t>
+          <t>58952; 76034</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13052; 19493</t>
+          <t>12889; 19277</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>334281; 370526</t>
+          <t>334325; 371849</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>395498; 434322</t>
+          <t>395522; 434952</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>378225; 417870</t>
+          <t>378016; 416858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69582; 83206</t>
+          <t>69641; 83413</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>364758; 401910</t>
+          <t>365922; 403847</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>420782; 462809</t>
+          <t>422581; 461586</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>395025; 437615</t>
+          <t>394233; 434283</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>94941; 110961</t>
+          <t>95748; 111241</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>710863; 763470</t>
+          <t>710826; 765220</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>827226; 885900</t>
+          <t>828572; 883455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>784716; 840387</t>
+          <t>785693; 843437</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>170886; 190848</t>
+          <t>169795; 190333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67,67%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>58,31%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>69,49%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>60,78%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80,62%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,25; 66,21</t>
+          <t>54,64; 70,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,82; 76,73</t>
+          <t>59,67; 75,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,45; 69,16</t>
+          <t>55,33; 71,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,19; 91,57</t>
+          <t>52,28; 89,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,8; 70,59</t>
+          <t>50,45; 66,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,68; 75,34</t>
+          <t>59,98; 76,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,97; 71,92</t>
+          <t>51,18; 69,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,01; 89,88</t>
+          <t>58,72; 90,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,55; 66,46</t>
+          <t>54,42; 66,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,69; 73,67</t>
+          <t>63,25; 74,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,24; 68,13</t>
+          <t>55,66; 68,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,72; 88,35</t>
+          <t>62,41; 87,27</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>59,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>62,15%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>80,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>58,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>60,34%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,87; 68,31</t>
+          <t>51,26; 68,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,04; 73,21</t>
+          <t>50,17; 66,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,86; 69,46</t>
+          <t>52,06; 68,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,23; 94,2</t>
+          <t>65,49; 96,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,6; 68,68</t>
+          <t>49,67; 68,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,79; 66,71</t>
+          <t>57,14; 73,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,62; 67,77</t>
+          <t>53,86; 70,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,25; 96,31</t>
+          <t>52,71; 94,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,09; 66,15</t>
+          <t>52,93; 65,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56,45; 68,33</t>
+          <t>56,02; 67,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,23; 66,76</t>
+          <t>55,05; 66,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,43; 93,11</t>
+          <t>68,55; 92,75</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,93%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>71,21%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>70,54%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>66,06%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77,66%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,1%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,32; 79,96</t>
+          <t>63,94; 79,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,62; 78,89</t>
+          <t>65,76; 81,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,33; 75,93</t>
+          <t>50,51; 69,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,78; 100,0</t>
+          <t>31,68; 82,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,6; 79,17</t>
+          <t>61,02; 79,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,36; 81,52</t>
+          <t>60,97; 77,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,02; 69,26</t>
+          <t>55,68; 75,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,75; 83,39</t>
+          <t>21,92; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,36; 77,48</t>
+          <t>65,32; 77,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,98; 78,19</t>
+          <t>66,04; 77,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,62; 69,49</t>
+          <t>55,98; 69,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,06; 82,74</t>
+          <t>39,42; 83,09</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>61,56%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>59,11%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>66,52%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,71; 67,17</t>
+          <t>58,34; 69,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,36; 65,02</t>
+          <t>57,79; 68,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,19; 71,7</t>
+          <t>61,2; 72,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,31; 85,7</t>
+          <t>69,43; 90,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,16; 69,23</t>
+          <t>55,61; 67,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,97; 68,21</t>
+          <t>53,61; 64,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,91; 72,02</t>
+          <t>61,23; 71,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68,66; 88,86</t>
+          <t>56,0; 83,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,34; 66,63</t>
+          <t>58,53; 66,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,67; 65,37</t>
+          <t>57,25; 64,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,89; 70,58</t>
+          <t>62,59; 70,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,4; 85,31</t>
+          <t>66,62; 84,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65,29%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>59,25%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>69,32%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>69,35%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>81,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>71,61%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -1277,42 +1277,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,24; 67,36</t>
+          <t>57,7; 72,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,95; 74,99</t>
+          <t>60,04; 73,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,52; 75,59</t>
+          <t>63,91; 77,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,34; 92,68</t>
+          <t>71,62; 93,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,3; 73,06</t>
+          <t>50,17; 67,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,17; 74,03</t>
+          <t>62,08; 75,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,91; 77,79</t>
+          <t>62,91; 75,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,88; 92,68</t>
+          <t>61,19; 91,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,48; 72,81</t>
+          <t>63,43; 73,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,79; 75,09</t>
+          <t>65,61; 75,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,87; 89,91</t>
+          <t>72,81; 90,67</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>65,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61,16%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79,75%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>72,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>61,62%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>54,26%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>80,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>61,91%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>80,43%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 80,32</t>
+          <t>56,34; 74,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,48; 71,5</t>
+          <t>51,83; 71,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,31; 65,8</t>
+          <t>49,98; 70,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,88; 95,64</t>
+          <t>52,0; 95,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,93; 74,75</t>
+          <t>63,46; 80,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,63; 71,89</t>
+          <t>49,55; 72,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,15; 71,08</t>
+          <t>43,64; 64,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,17; 95,11</t>
+          <t>51,19; 96,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,61; 75,37</t>
+          <t>62,03; 75,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55,13; 69,13</t>
+          <t>54,3; 68,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50,07; 64,58</t>
+          <t>50,08; 64,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61,29; 91,67</t>
+          <t>63,76; 92,49</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64,95%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65,21%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65,14%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>62,76%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>65,25%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>64,54%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,5; 66,17</t>
+          <t>61,74; 67,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,08; 68,26</t>
+          <t>62,12; 68,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,36; 67,66</t>
+          <t>61,92; 68,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70,57; 84,53</t>
+          <t>72,71; 84,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,76; 68,16</t>
+          <t>59,42; 65,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,3; 68,05</t>
+          <t>62,0; 68,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,77; 68,05</t>
+          <t>61,41; 67,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,45; 85,33</t>
+          <t>68,66; 83,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,57; 66,28</t>
+          <t>61,44; 65,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,99; 67,16</t>
+          <t>63,27; 67,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,64; 67,24</t>
+          <t>62,71; 67,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,13; 83,1</t>
+          <t>73,9; 82,66</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1801,32 +1801,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>54187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58099</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59371</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13948</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>55105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>58296</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>46648</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19972</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54187</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58099</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59371</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>30779</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47489; 62570</t>
+          <t>47055; 61065</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50185; 64370</t>
+          <t>51235; 65143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39486; 53074</t>
+          <t>51429; 66518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15654; 22684</t>
+          <t>9885; 16931</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46331; 60789</t>
+          <t>47677; 62591</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50383; 64688</t>
+          <t>50323; 64438</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52023; 66854</t>
+          <t>39274; 53281</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11297; 18460</t>
+          <t>12745; 19597</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98519; 120042</t>
+          <t>98297; 120005</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104714; 125059</t>
+          <t>107362; 125990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95431; 115606</t>
+          <t>94455; 115734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29780; 40031</t>
+          <t>25345; 35443</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45482</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>51932</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59057</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13366</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>47836</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>58604</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>59931</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8437</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45482</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51932</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59057</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>21524</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40839; 54846</t>
+          <t>38636; 51873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51001; 65461</t>
+          <t>44242; 58989</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51934; 66985</t>
+          <t>50958; 67042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5375; 9883</t>
+          <t>10333; 15157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38133; 51760</t>
+          <t>39876; 54804</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43910; 58829</t>
+          <t>51091; 65904</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49548; 66334</t>
+          <t>51940; 67530</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11054; 15598</t>
+          <t>5383; 9660</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84197; 102958</t>
+          <t>82384; 102366</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100259; 121369</t>
+          <t>99502; 120332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107321; 129728</t>
+          <t>106965; 130001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18797; 24849</t>
+          <t>17817; 24107</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>61455</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40567</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5886</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>42789</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>57584</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61455</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61331</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40567</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>8341</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36845; 48049</t>
+          <t>54659; 67910</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50303; 64399</t>
+          <t>54556; 67840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29651; 40691</t>
+          <t>34097; 46920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>846; 3415</t>
+          <t>3121; 8105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54368; 67679</t>
+          <t>36664; 47894</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54226; 67633</t>
+          <t>49772; 63347</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33765; 46754</t>
+          <t>29840; 40636</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3687; 9111</t>
+          <t>699; 3189</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>95143; 112798</t>
+          <t>95087; 112683</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>110249; 128698</t>
+          <t>108690; 127778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67351; 84145</t>
+          <t>67793; 84618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5745; 11866</t>
+          <t>5140; 10836</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>113156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136827</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126475</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30965</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>106143</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>113842</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>137956</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22145</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>113156</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>136827</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>126475</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33345</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>51728</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96061; 115826</t>
+          <t>102966; 122984</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102770; 125212</t>
+          <t>125214; 147598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126904; 148697</t>
+          <t>115675; 136633</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17914; 25882</t>
+          <t>26495; 34628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>102639; 122183</t>
+          <t>95887; 116742</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>125607; 147793</t>
+          <t>103248; 124875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115127; 136128</t>
+          <t>126985; 148334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28240; 36549</t>
+          <t>16395; 24592</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>203570; 232483</t>
+          <t>204211; 233658</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>236033; 267528</t>
+          <t>234301; 265640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>249295; 279764</t>
+          <t>248103; 279353</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48788; 60851</t>
+          <t>44925; 56671</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>90539</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>92682</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23352</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>50856</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>94946</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>87112</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16608</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67052</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90539</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92682</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>39525</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43126; 57816</t>
+          <t>59257; 74317</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84851; 102715</t>
+          <t>80729; 99427</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78529; 94953</t>
+          <t>82726; 100876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12949; 18946</t>
+          <t>19660; 25620</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59875; 75031</t>
+          <t>43061; 57739</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80911; 99542</t>
+          <t>85026; 103449</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84021; 100688</t>
+          <t>79023; 94893</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21493; 27710</t>
+          <t>12186; 18214</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107017; 128154</t>
+          <t>107018; 128150</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>172294; 197639</t>
+          <t>172181; 198342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>167790; 191515</t>
+          <t>167323; 191576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36683; 45264</t>
+          <t>34486; 42944</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>43532</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43548</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37570</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>49953</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>32449</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>30553</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>43532</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43548</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>37570</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16148</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43842; 55238</t>
+          <t>37399; 49484</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25529; 37652</t>
+          <t>36328; 49947</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24385; 37049</t>
+          <t>30703; 43268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4948; 8948</t>
+          <t>5456; 10026</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36459; 49619</t>
+          <t>43639; 55241</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36190; 50387</t>
+          <t>26092; 37939</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31422; 43665</t>
+          <t>24571; 36559</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5738; 11101</t>
+          <t>4907; 9243</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84617; 101862</t>
+          <t>83831; 101672</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67678; 84854</t>
+          <t>66653; 84556</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58952; 76034</t>
+          <t>58966; 76510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12889; 19277</t>
+          <t>12801; 18569</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>521</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>384863</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>442275</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>415722</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>95883</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>352682</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>415722</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>397602</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>384863</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>442275</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>415722</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>104019</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>181353</t>
+          <t>168045</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>334325; 371849</t>
+          <t>365834; 402398</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>395522; 434952</t>
+          <t>421350; 462835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>378016; 416858</t>
+          <t>395181; 435422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69641; 83413</t>
+          <t>87716; 102275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>365922; 403847</t>
+          <t>333915; 369611</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>422581; 461586</t>
+          <t>395043; 434525</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>394233; 434283</t>
+          <t>378335; 415859</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>95748; 111241</t>
+          <t>64465; 78555</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>710826; 765220</t>
+          <t>709349; 761583</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828572; 883455</t>
+          <t>832291; 889692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>785693; 843437</t>
+          <t>786551; 842287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>169795; 190333</t>
+          <t>158539; 177318</t>
         </is>
       </c>
     </row>
